--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,265 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120227440</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnholmen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554091</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6582066</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120227193</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnholmen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554072</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6582011</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avverkningsanmäld barrskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120227440</v>
+        <v>120227193</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,40 +795,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554091</v>
+        <v>554072</v>
       </c>
       <c r="R3" t="n">
-        <v>6582066</v>
+        <v>6582011</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -871,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
+          <t>Avverkningsanmäld barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120227193</v>
+        <v>120227440</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +924,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554072</v>
+        <v>554091</v>
       </c>
       <c r="R4" t="n">
-        <v>6582011</v>
+        <v>6582066</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avverkningsanmäld barrskog.</t>
+          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120227193</v>
+        <v>120227440</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,39 +795,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554072</v>
+        <v>554091</v>
       </c>
       <c r="R3" t="n">
-        <v>6582011</v>
+        <v>6582066</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Avverkningsanmäld barrskog.</t>
+          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120227440</v>
+        <v>120227193</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,40 +925,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554091</v>
+        <v>554072</v>
       </c>
       <c r="R4" t="n">
-        <v>6582066</v>
+        <v>6582011</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
+          <t>Avverkningsanmäld barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120227440</v>
+        <v>120227193</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,40 +795,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554091</v>
+        <v>554072</v>
       </c>
       <c r="R3" t="n">
-        <v>6582066</v>
+        <v>6582011</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -871,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
+          <t>Avverkningsanmäld barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120227193</v>
+        <v>120227440</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +924,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554072</v>
+        <v>554091</v>
       </c>
       <c r="R4" t="n">
-        <v>6582011</v>
+        <v>6582066</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avverkningsanmäld barrskog.</t>
+          <t>Gnagspår på granlågor. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>121120955</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>121120955</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>121120955</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>121120955</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1169,117 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126253651</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gustavs holme, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>554071</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6581994</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Frida Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36185-2024 artfynd.xlsx
+++ b/artfynd/A 36185-2024 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>126253651</v>
       </c>
       <c r="B6" t="n">
-        <v>45049</v>
+        <v>45050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
